--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260715.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.92%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.23%</t>
+          <t>10.33%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.62%</t>
+          <t>8.79%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>7.37%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.55%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>33,514</t>
+          <t>51,605</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>51,605</t>
+          <t>33,514</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>44,825</t>
+          <t>13,838</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,838</t>
+          <t>44,825</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>98,148,028</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
